--- a/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>10930</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>6329</v>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>17258</v>
+          <t>1706</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10449</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>10877</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>17910</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>93532</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>130579</v>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>303</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>224112</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>6381</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>12226</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>104462</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93532</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87397</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>136908</v>
+          <t>89,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>83,66%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>93,74%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>163</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>130579</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>328</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>241370</v>
+          <t>124805</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>134502</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>224112</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>216204</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>230193</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>89,57%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Grupo III</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>4398</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104462</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>10285</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>136908</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>14682</v>
+          <t>136908</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>136908</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>241370</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>241370</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>241370</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>90283</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>117</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>85288</v>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>175572</v>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>14577</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>10949</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>17288</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>94681</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>95573</v>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>190254</v>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7810</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7941</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>3187</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90283</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>85784</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>92828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>4721</v>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>117</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>85288</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>7908</v>
+          <t>78781</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>89781</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>175572</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>168373</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>181031</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>88,5%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>48674</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94681</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94681</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>94681</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>59132</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>95573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>107806</v>
+          <t>95573</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>95573</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>190254</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>51861</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>63853</v>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>115714</v>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8221</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VI</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>9716</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>15008</v>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>24724</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2607</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>262</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>208294</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48674</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>203264</v>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>59132</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>525</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>411558</v>
+          <t>54132</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>61677</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,61%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>107806</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>102445</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>111392</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>277</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>218010</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51861</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>51861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>285</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>218272</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>63853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>562</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>436282</v>
+          <t>63853</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>63853</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>115714</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Grupo VII</t>
+          <t>Grupo VI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>13451</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7390</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>15714</v>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>29165</v>
+          <t>6834</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18587</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>19126</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>12096</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>27240</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>105977</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>146903</v>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>336</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>252880</v>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>7592</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>5598</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>10756</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -1677,216 +2309,342 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>119428</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>208294</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>201833</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>212860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>162617</v>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>263</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>203264</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>378</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>282045</v>
+          <t>195676</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>208847</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>93,12%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>411558</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>402363</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>419502</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>92,23%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>4435</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>218010</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>218010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>218010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>4581</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>285</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>218272</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>9017</v>
+          <t>218272</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>218272</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>436282</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>64460</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10277</t>
+        </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>67422</v>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>131881</v>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>21292</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>21919</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>14331</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>30807</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1894,145 +2652,225 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>68895</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>72003</v>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>140898</v>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9921</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>7246</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>3503</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>13419</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>46117</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>105977</t>
+        </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>110593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>56638</v>
+          <t>88,74%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>83,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>146903</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>102755</v>
+          <t>136775</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>153043</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>90,34%</t>
+        </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>252880</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>242499</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>261237</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -2040,146 +2878,1029 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>854</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>611220</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>119428</t>
+        </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>119428</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>119428</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>882</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>692587</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>198</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>162617</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1736</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>1303808</v>
+          <t>162617</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>162617</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>282045</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>929</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>657337</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>959</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>749225</v>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>1888</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>1406563</v>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8564</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>7030</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>64460</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>60051</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>66734</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>87,16%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>67422</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>63034</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>70525</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>131881</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>126101</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>135657</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>89,5%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68895</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>140898</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>32134</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>24518</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>42784</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>43069</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>32287</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>55856</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>75204</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>61589</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>91940</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13983</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>8723</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>21077</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>7895</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>21191</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>27551</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>19387</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>37461</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>611220</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>599277</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>621007</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>92,98%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>692587</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>677924</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>704981</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1736</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1303808</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1285277</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1319340</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>92,69%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>91,38%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>93,8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>657337</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>749225</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>749225</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>749225</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1406563</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1406563</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>1406563</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -2187,17 +3908,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87397</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97922</t>
+          <t>98043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124805</t>
+          <t>124674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134502</t>
+          <t>134117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216204</t>
+          <t>214900</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>230193</t>
+          <t>229824</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92828</t>
+          <t>92799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>78820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>90030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168373</t>
+          <t>167994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181031</t>
+          <t>181089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45146</t>
+          <t>45066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>50598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54132</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102445</t>
+          <t>102392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111392</t>
+          <t>111875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>11971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>27405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>201833</t>
+          <t>201644</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212860</t>
+          <t>212925</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>195676</t>
+          <t>194814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208847</t>
+          <t>208888</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>402363</t>
+          <t>402357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419502</t>
+          <t>419653</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2667,47 +2667,47 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>7242</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1423</t>
-        </is>
-      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99226</t>
+          <t>99695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>110593</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136775</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153043</t>
+          <t>153324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242499</t>
+          <t>242017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261237</t>
+          <t>261417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>66896</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63034</t>
+          <t>62724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70525</t>
+          <t>70156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126101</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24518</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42784</t>
+          <t>43048</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61589</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91940</t>
+          <t>91862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21153</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37461</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>599277</t>
+          <t>598754</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>621007</t>
+          <t>621744</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>677924</t>
+          <t>678086</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>704981</t>
+          <t>705583</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1285277</t>
+          <t>1285468</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1319340</t>
+          <t>1321409</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11655</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4631</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9864</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116694</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>111797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>120181</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>91,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>93532</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>87379</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>98043</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130579</t>
+          <t>91622</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124674</t>
+          <t>85297</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134117</t>
+          <t>96121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>224112</t>
+          <t>208317</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214900</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>229824</t>
+          <t>214401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3277</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7408</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2668</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7409</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3712</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6863</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>81131</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75003</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>85738</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90283</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85952</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92799</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85288</t>
+          <t>92409</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175572</t>
+          <t>173540</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167994</t>
+          <t>165371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181089</t>
+          <t>178467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94681</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190254</t>
+          <t>187944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7716</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>48244</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55245</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>48674</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45066</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50598</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>50507</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54632</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61876</t>
+          <t>52347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>107806</t>
+          <t>103244</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102392</t>
+          <t>97853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>111875</t>
+          <t>106516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10601</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16916</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7390</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3709</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27405</t>
+          <t>25878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3061</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7776</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>6399</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>188282</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>181161</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>193384</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>89,71%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>208294</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>201644</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>212925</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>92,49%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>203264</t>
+          <t>169270</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194814</t>
+          <t>163383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208888</t>
+          <t>173150</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>411558</t>
+          <t>357552</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>402357</t>
+          <t>348342</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>419653</t>
+          <t>364325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10784</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5909</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19385</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10277</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5813</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15864</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>21919</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -2662,102 +2662,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>7835</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>3562</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>13351</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>4072</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9467</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>7246</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>3427</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>13463</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>133565</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>124620</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>139645</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,2%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>105977</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>99695</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>110795</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>88,74%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>146903</t>
+          <t>105904</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>137436</t>
+          <t>99483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153324</t>
+          <t>110783</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>252880</t>
+          <t>239469</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>242017</t>
+          <t>227986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261417</t>
+          <t>247255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>148243</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162617</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282045</t>
+          <t>266974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>8928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -3113,72 +3113,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2973</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3719</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>334</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>63649</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>58885</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>66786</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>64460</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>60763</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>66896</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>88,2%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67422</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70156</t>
+          <t>68190</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>131881</t>
+          <t>129312</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>123492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>136340</t>
+          <t>133284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>40203</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>30009</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>52364</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>32134</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>24477</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>43048</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>41283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>71792</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>58828</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91862</t>
+          <t>87431</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7770</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>20801</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>13983</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>8824</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>21490</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>36837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>636057</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>621813</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>647106</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>93,87%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>854</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>611220</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>598754</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>621744</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>692587</t>
+          <t>575376</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>678086</t>
+          <t>564687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>705583</t>
+          <t>585134</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1303808</t>
+          <t>1211433</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1285468</t>
+          <t>1195600</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1321409</t>
+          <t>1227339</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>689387</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>657337</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>749225</t>
+          <t>620857</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1406563</t>
+          <t>1310244</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1406563</t>
+          <t>1310244</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1406563</t>
+          <t>1310244</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
